--- a/Results_experiment/exp_2/preds_1114422222322222.xlsx
+++ b/Results_experiment/exp_2/preds_1114422222322222.xlsx
@@ -1245,7 +1245,7 @@
         <v>-3</v>
       </c>
       <c r="D2">
-        <v>-0.6420138478279114</v>
+        <v>-0.65828537940979</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1259,7 +1259,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D3">
-        <v>0.1623389422893524</v>
+        <v>0.5546125173568726</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1273,7 +1273,7 @@
         <v>-3</v>
       </c>
       <c r="D4">
-        <v>-1.18485164642334</v>
+        <v>-1.224240779876709</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1287,7 +1287,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D5">
-        <v>-0.9156476855278015</v>
+        <v>-0.8454222679138184</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1301,7 +1301,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D6">
-        <v>-1.123849868774414</v>
+        <v>-1.506550550460815</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1315,7 +1315,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D7">
-        <v>0.5863994956016541</v>
+        <v>0.9922184944152832</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1329,7 +1329,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D8">
-        <v>2.376761198043823</v>
+        <v>3.348023176193237</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1343,7 +1343,7 @@
         <v>-4.5</v>
       </c>
       <c r="D9">
-        <v>-1.304933309555054</v>
+        <v>-0.4776669442653656</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1357,7 +1357,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D10">
-        <v>1.001958847045898</v>
+        <v>0.9483397006988525</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1371,7 +1371,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D11">
-        <v>0.9770233035087585</v>
+        <v>1.586186289787292</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1385,7 +1385,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D12">
-        <v>0.6669634580612183</v>
+        <v>0.7971712350845337</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1399,7 +1399,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D13">
-        <v>0.9776428937911987</v>
+        <v>1.099103927612305</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1413,7 +1413,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D14">
-        <v>-0.003446966409683228</v>
+        <v>0.1281725168228149</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1427,7 +1427,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D15">
-        <v>1.919915199279785</v>
+        <v>2.420084714889526</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1441,7 +1441,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D16">
-        <v>-3.441638231277466</v>
+        <v>-3.026428461074829</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1455,7 +1455,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D17">
-        <v>0.1191695034503937</v>
+        <v>0.2255770862102509</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1469,7 +1469,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D18">
-        <v>0.9265993237495422</v>
+        <v>1.43609619140625</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1483,7 +1483,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D19">
-        <v>-1.020602941513062</v>
+        <v>-1.166796207427979</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1497,7 +1497,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D20">
-        <v>-0.5699346661567688</v>
+        <v>0.01564392447471619</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1511,7 +1511,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D21">
-        <v>1.145152807235718</v>
+        <v>1.396466493606567</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1525,7 +1525,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D22">
-        <v>3.428438186645508</v>
+        <v>3.160571098327637</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1539,7 +1539,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D23">
-        <v>3.3209388256073</v>
+        <v>2.871108770370483</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1553,7 +1553,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D24">
-        <v>-0.3986626267433167</v>
+        <v>-0.1958190500736237</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1567,7 +1567,7 @@
         <v>0.5</v>
       </c>
       <c r="D25">
-        <v>0.4473455548286438</v>
+        <v>1.063583374023438</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1581,7 +1581,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D26">
-        <v>-2.770487785339355</v>
+        <v>-2.613513231277466</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1595,7 +1595,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D27">
-        <v>0.5643412470817566</v>
+        <v>0.3512557446956635</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1609,7 +1609,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>0.5858811140060425</v>
+        <v>0.1824358403682709</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1623,7 +1623,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D29">
-        <v>-0.2543403506278992</v>
+        <v>0.2558639645576477</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1637,7 +1637,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D30">
-        <v>-0.985041081905365</v>
+        <v>-1.238517045974731</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1651,7 +1651,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D31">
-        <v>1.365432024002075</v>
+        <v>1.391015291213989</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1665,7 +1665,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D32">
-        <v>4.586941719055176</v>
+        <v>5.615664482116699</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1679,7 +1679,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D33">
-        <v>1.003979682922363</v>
+        <v>0.7091561555862427</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1693,7 +1693,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D34">
-        <v>0.2633755505084991</v>
+        <v>0.08040042966604233</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1707,7 +1707,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>-2.093828201293945</v>
+        <v>-2.410985708236694</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1721,7 +1721,7 @@
         <v>19.20000076293945</v>
       </c>
       <c r="D36">
-        <v>14.56754398345947</v>
+        <v>13.29541301727295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1735,7 +1735,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D37">
-        <v>1.210459470748901</v>
+        <v>0.7982792854309082</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1749,7 +1749,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D38">
-        <v>-0.1579137444496155</v>
+        <v>-0.09724339842796326</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1763,7 +1763,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D39">
-        <v>2.157268047332764</v>
+        <v>2.709245920181274</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1777,7 +1777,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D40">
-        <v>0.08551478385925293</v>
+        <v>0.7097691297531128</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1791,7 +1791,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D41">
-        <v>0.01856815814971924</v>
+        <v>-0.9301514625549316</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1805,7 +1805,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D42">
-        <v>2.309273481369019</v>
+        <v>2.535889863967896</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1819,7 +1819,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D43">
-        <v>0.4261147677898407</v>
+        <v>0.2702275514602661</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1833,7 +1833,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D44">
-        <v>4.678924560546875</v>
+        <v>5.169094562530518</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1847,7 +1847,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D45">
-        <v>0.17498978972435</v>
+        <v>0.09163796901702881</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1861,7 +1861,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D46">
-        <v>1.208625316619873</v>
+        <v>1.447415709495544</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1875,7 +1875,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D47">
-        <v>1.004750847816467</v>
+        <v>0.3922438025474548</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1889,7 +1889,7 @@
         <v>3.5</v>
       </c>
       <c r="D48">
-        <v>2.436317920684814</v>
+        <v>2.41045355796814</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1903,7 +1903,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D49">
-        <v>-2.502686023712158</v>
+        <v>-2.015389204025269</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1917,7 +1917,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D50">
-        <v>2.863841772079468</v>
+        <v>2.409789800643921</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1931,7 +1931,7 @@
         <v>-2</v>
       </c>
       <c r="D51">
-        <v>0.7393136024475098</v>
+        <v>0.322907567024231</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1945,7 +1945,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D52">
-        <v>0.9952804446220398</v>
+        <v>1.084172368049622</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1959,7 +1959,7 @@
         <v>-7</v>
       </c>
       <c r="D53">
-        <v>-0.7789224982261658</v>
+        <v>-0.7938519716262817</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1973,7 +1973,7 @@
         <v>-2.5</v>
       </c>
       <c r="D54">
-        <v>-0.5679842829704285</v>
+        <v>-0.9617903232574463</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1987,7 +1987,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D55">
-        <v>-1.688624858856201</v>
+        <v>-1.47907543182373</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2001,7 +2001,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D56">
-        <v>2.073967933654785</v>
+        <v>1.435739994049072</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2015,7 +2015,7 @@
         <v>-10.19999980926514</v>
       </c>
       <c r="D57">
-        <v>-7.729700565338135</v>
+        <v>-5.933284282684326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2029,7 +2029,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D58">
-        <v>0.1053886711597443</v>
+        <v>0.2793789803981781</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2043,7 +2043,7 @@
         <v>2.5</v>
       </c>
       <c r="D59">
-        <v>1.487113237380981</v>
+        <v>1.252689599990845</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2057,7 +2057,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D60">
-        <v>4.198107719421387</v>
+        <v>4.46644115447998</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2071,7 +2071,7 @@
         <v>-0.5</v>
       </c>
       <c r="D61">
-        <v>0.1771893948316574</v>
+        <v>-0.01018783450126648</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2085,7 +2085,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D62">
-        <v>-6.259115219116211</v>
+        <v>-6.502353191375732</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2099,7 +2099,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D63">
-        <v>0.9149792790412903</v>
+        <v>0.2789637744426727</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2113,7 +2113,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D64">
-        <v>0.8965614438056946</v>
+        <v>0.7221788167953491</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2127,7 +2127,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D65">
-        <v>-0.4784281253814697</v>
+        <v>-0.1194851696491241</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2141,7 +2141,7 @@
         <v>-1.5</v>
       </c>
       <c r="D66">
-        <v>-1.444289922714233</v>
+        <v>-0.8995616436004639</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2155,7 +2155,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D67">
-        <v>2.213398933410645</v>
+        <v>2.423054456710815</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2169,7 +2169,7 @@
         <v>5.5</v>
       </c>
       <c r="D68">
-        <v>2.508634090423584</v>
+        <v>4.327084064483643</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2183,7 +2183,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D69">
-        <v>0.863162100315094</v>
+        <v>1.088355779647827</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2197,7 +2197,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D70">
-        <v>-0.306010901927948</v>
+        <v>-0.8017187118530273</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2211,7 +2211,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D71">
-        <v>1.605211496353149</v>
+        <v>1.075336575508118</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2225,7 +2225,7 @@
         <v>3.5</v>
       </c>
       <c r="D72">
-        <v>2.639870643615723</v>
+        <v>2.943087339401245</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2239,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>1.079822063446045</v>
+        <v>0.555864691734314</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2253,7 +2253,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>-0.8621253371238708</v>
+        <v>-1.253234148025513</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2267,7 +2267,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D75">
-        <v>5.052484035491943</v>
+        <v>3.888955593109131</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2281,7 +2281,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D76">
-        <v>0.2265016138553619</v>
+        <v>0.189865306019783</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2295,7 +2295,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D77">
-        <v>2.791044473648071</v>
+        <v>2.533525705337524</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2309,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="D78">
-        <v>1.616486549377441</v>
+        <v>2.282737493515015</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2323,7 +2323,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D79">
-        <v>3.548934459686279</v>
+        <v>2.835701704025269</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2337,7 +2337,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D80">
-        <v>-1.87792444229126</v>
+        <v>-2.730481624603271</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2351,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>4.127173900604248</v>
+        <v>3.423382997512817</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2365,7 +2365,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D82">
-        <v>-0.1680857539176941</v>
+        <v>-0.8657271862030029</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2379,7 +2379,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D83">
-        <v>-3.529428005218506</v>
+        <v>-3.143175363540649</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>2.72047758102417</v>
+        <v>3.182055950164795</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2407,7 +2407,7 @@
         <v>-21</v>
       </c>
       <c r="D85">
-        <v>-15.20126342773438</v>
+        <v>-17.38978004455566</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2421,7 +2421,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D86">
-        <v>-0.2400930523872375</v>
+        <v>0.003235951066017151</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2435,7 +2435,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D87">
-        <v>0.09975859522819519</v>
+        <v>0.1282232105731964</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2449,7 +2449,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D88">
-        <v>2.771681547164917</v>
+        <v>2.535035848617554</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2463,7 +2463,7 @@
         <v>-3</v>
       </c>
       <c r="D89">
-        <v>0.3098006844520569</v>
+        <v>0.2038604617118835</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2477,7 +2477,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D90">
-        <v>0.7792654037475586</v>
+        <v>1.170271873474121</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2491,7 +2491,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D91">
-        <v>0.5213595628738403</v>
+        <v>0.2626956701278687</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2505,7 +2505,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D92">
-        <v>-1.425758600234985</v>
+        <v>-2.455283641815186</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2519,7 +2519,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D93">
-        <v>0.9589452147483826</v>
+        <v>1.2093745470047</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2533,7 +2533,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D94">
-        <v>0.7896809577941895</v>
+        <v>0.3927810192108154</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2547,7 +2547,7 @@
         <v>-2</v>
       </c>
       <c r="D95">
-        <v>-0.9304823279380798</v>
+        <v>-0.617112398147583</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2561,7 +2561,7 @@
         <v>-1.5</v>
       </c>
       <c r="D96">
-        <v>0.5717722177505493</v>
+        <v>0.3494043350219727</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2575,7 +2575,7 @@
         <v>3</v>
       </c>
       <c r="D97">
-        <v>2.482309818267822</v>
+        <v>3.289686679840088</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2589,7 +2589,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D98">
-        <v>2.402583599090576</v>
+        <v>1.134509444236755</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2603,7 +2603,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D99">
-        <v>0.1053246557712555</v>
+        <v>0.1165750250220299</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2617,7 +2617,7 @@
         <v>-0.5</v>
       </c>
       <c r="D100">
-        <v>0.2552709579467773</v>
+        <v>0.166406124830246</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2631,7 +2631,7 @@
         <v>-1.5</v>
       </c>
       <c r="D101">
-        <v>0.008406549692153931</v>
+        <v>0.4598041474819183</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2645,7 +2645,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D102">
-        <v>0.920225203037262</v>
+        <v>2.121914148330688</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2659,7 +2659,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D103">
-        <v>2.754347801208496</v>
+        <v>4.33065128326416</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2673,7 +2673,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D104">
-        <v>5.132621288299561</v>
+        <v>5.671547412872314</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D105">
-        <v>2.071710824966431</v>
+        <v>1.124407529830933</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2701,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>-0.8046186566352844</v>
+        <v>-0.2655121982097626</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2715,7 +2715,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>1.255457162857056</v>
+        <v>1.100181102752686</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2729,7 +2729,7 @@
         <v>2.5</v>
       </c>
       <c r="D108">
-        <v>1.37566614151001</v>
+        <v>1.653661012649536</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2743,7 +2743,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>1.481340885162354</v>
+        <v>1.79725182056427</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2757,7 +2757,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D110">
-        <v>8.676618576049805</v>
+        <v>6.088825702667236</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2771,7 +2771,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D111">
-        <v>1.369522571563721</v>
+        <v>0.5935119390487671</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2785,7 +2785,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>-0.1668849587440491</v>
+        <v>0.342497318983078</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2799,7 +2799,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D113">
-        <v>0.1867203712463379</v>
+        <v>0.1723106950521469</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2813,7 +2813,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D114">
-        <v>0.3777157962322235</v>
+        <v>0.3150686621665955</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2827,7 +2827,7 @@
         <v>0.5</v>
       </c>
       <c r="D115">
-        <v>0.2449049949645996</v>
+        <v>-0.05303359031677246</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>1.266746997833252</v>
+        <v>1.229941844940186</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2855,7 +2855,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D117">
-        <v>0.6377335786819458</v>
+        <v>1.412216663360596</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2869,7 +2869,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D118">
-        <v>2.511656761169434</v>
+        <v>2.609260320663452</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2883,7 +2883,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D119">
-        <v>0.9966151714324951</v>
+        <v>0.4812359511852264</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2897,7 +2897,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D120">
-        <v>1.366132736206055</v>
+        <v>1.900500774383545</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2911,7 +2911,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D121">
-        <v>2.357967376708984</v>
+        <v>2.686856031417847</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2925,7 +2925,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D122">
-        <v>2.226094007492065</v>
+        <v>2.236209630966187</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2939,7 +2939,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D123">
-        <v>1.262034177780151</v>
+        <v>1.265646696090698</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2953,7 +2953,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D124">
-        <v>1.105655193328857</v>
+        <v>1.242087960243225</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2967,7 +2967,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D125">
-        <v>1.558837413787842</v>
+        <v>1.975023150444031</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2981,7 +2981,7 @@
         <v>-18.29999923706055</v>
       </c>
       <c r="D126">
-        <v>-12.70236301422119</v>
+        <v>-12.91131496429443</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D127">
-        <v>1.364249467849731</v>
+        <v>1.129120230674744</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3009,7 +3009,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D128">
-        <v>-0.4737067818641663</v>
+        <v>-0.412250429391861</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3023,7 +3023,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D129">
-        <v>0.07856041193008423</v>
+        <v>0.1756737232208252</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3037,7 +3037,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D130">
-        <v>0.4431248903274536</v>
+        <v>0.06961113214492798</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3051,7 +3051,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D131">
-        <v>0.2985136806964874</v>
+        <v>0.1299203485250473</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3065,7 +3065,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D132">
-        <v>-2.627254009246826</v>
+        <v>-2.64764666557312</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3079,7 +3079,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>4.070086002349854</v>
+        <v>5.07768726348877</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3093,7 +3093,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D134">
-        <v>0.2100327163934708</v>
+        <v>0.09882082045078278</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3107,7 +3107,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D135">
-        <v>-2.327118396759033</v>
+        <v>-1.830042123794556</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3121,7 +3121,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D136">
-        <v>5.152231693267822</v>
+        <v>5.260426998138428</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3135,7 +3135,7 @@
         <v>2.5</v>
       </c>
       <c r="D137">
-        <v>0.8245497345924377</v>
+        <v>1.743583679199219</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3149,7 +3149,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D138">
-        <v>1.299112558364868</v>
+        <v>1.542961597442627</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3163,7 +3163,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D139">
-        <v>2.182473659515381</v>
+        <v>2.262746810913086</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3177,7 +3177,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D140">
-        <v>-0.4121178984642029</v>
+        <v>0.04301668703556061</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3191,7 +3191,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D141">
-        <v>2.006101131439209</v>
+        <v>2.093433856964111</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3205,7 +3205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D142">
-        <v>2.752464056015015</v>
+        <v>2.424296617507935</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3219,7 +3219,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D143">
-        <v>1.227142572402954</v>
+        <v>1.642165899276733</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3233,7 +3233,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D144">
-        <v>1.483838081359863</v>
+        <v>1.685554385185242</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3247,7 +3247,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>0.6275677680969238</v>
+        <v>0.5359659194946289</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3261,7 +3261,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D146">
-        <v>1.105738401412964</v>
+        <v>1.019137382507324</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3275,7 +3275,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D147">
-        <v>2.472152709960938</v>
+        <v>2.260407686233521</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3289,7 +3289,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>-1.075491189956665</v>
+        <v>-1.112987279891968</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D149">
-        <v>0.9293137192726135</v>
+        <v>1.235865354537964</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3317,7 +3317,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D150">
-        <v>2.084325075149536</v>
+        <v>1.166243076324463</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3331,7 +3331,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D151">
-        <v>-3.019599914550781</v>
+        <v>-2.940613508224487</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3345,7 +3345,7 @@
         <v>-11</v>
       </c>
       <c r="D152">
-        <v>-7.338077068328857</v>
+        <v>-7.851442813873291</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3359,7 +3359,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D153">
-        <v>1.954596519470215</v>
+        <v>1.684634685516357</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3373,7 +3373,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D154">
-        <v>-0.4307877421379089</v>
+        <v>-0.1495798230171204</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3387,7 +3387,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D155">
-        <v>1.568853855133057</v>
+        <v>1.388746619224548</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3401,7 +3401,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D156">
-        <v>1.073960781097412</v>
+        <v>0.3898483216762543</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3415,7 +3415,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D157">
-        <v>1.106362104415894</v>
+        <v>1.146101832389832</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3429,7 +3429,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D158">
-        <v>3.444230079650879</v>
+        <v>2.885456800460815</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3443,7 +3443,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D159">
-        <v>-0.483683168888092</v>
+        <v>0.05432675778865814</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3457,7 +3457,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D160">
-        <v>-0.4763501882553101</v>
+        <v>-0.5427863597869873</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3471,7 +3471,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>1.714076519012451</v>
+        <v>1.265135169029236</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3485,7 +3485,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D162">
-        <v>-3.134330034255981</v>
+        <v>-2.260455369949341</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3499,7 +3499,7 @@
         <v>1.5</v>
       </c>
       <c r="D163">
-        <v>-0.574914276599884</v>
+        <v>-0.2045067250728607</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3513,7 +3513,7 @@
         <v>0.5</v>
       </c>
       <c r="D164">
-        <v>0.4344294369220734</v>
+        <v>0.236351490020752</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3527,7 +3527,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D165">
-        <v>1.401732444763184</v>
+        <v>1.116002082824707</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3541,7 +3541,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D166">
-        <v>2.579832077026367</v>
+        <v>1.915028095245361</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3555,7 +3555,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>1.759119510650635</v>
+        <v>1.280159473419189</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3569,7 +3569,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D168">
-        <v>0.8022507429122925</v>
+        <v>0.8428248167037964</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3583,7 +3583,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D169">
-        <v>0.7377433776855469</v>
+        <v>0.1620827168226242</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3597,7 +3597,7 @@
         <v>-6</v>
       </c>
       <c r="D170">
-        <v>-2.048659563064575</v>
+        <v>-2.307100057601929</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3611,7 +3611,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D171">
-        <v>1.582322359085083</v>
+        <v>1.95207142829895</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3625,7 +3625,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D172">
-        <v>1.118698716163635</v>
+        <v>1.151280641555786</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3639,7 +3639,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D173">
-        <v>2.382798194885254</v>
+        <v>2.216049194335938</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3653,7 +3653,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D174">
-        <v>1.170933485031128</v>
+        <v>0.861059308052063</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3667,7 +3667,7 @@
         <v>2.5</v>
       </c>
       <c r="D175">
-        <v>2.621379613876343</v>
+        <v>2.103606224060059</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3681,7 +3681,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D176">
-        <v>0.5632820129394531</v>
+        <v>0.384813517332077</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3695,7 +3695,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D177">
-        <v>-0.8917631506919861</v>
+        <v>0.7032017707824707</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3709,7 +3709,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D178">
-        <v>0.7285640239715576</v>
+        <v>0.5772124528884888</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3723,7 +3723,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D179">
-        <v>2.984288215637207</v>
+        <v>3.069113969802856</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3737,7 +3737,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D180">
-        <v>0.8340818285942078</v>
+        <v>0.2645540237426758</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3751,7 +3751,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D181">
-        <v>0.2090750634670258</v>
+        <v>0.1773931533098221</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3765,7 +3765,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D182">
-        <v>-1.489879846572876</v>
+        <v>-0.2681254744529724</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3779,7 +3779,7 @@
         <v>-0.5</v>
       </c>
       <c r="D183">
-        <v>-0.6868379712104797</v>
+        <v>-0.5503536462783813</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3793,7 +3793,7 @@
         <v>5</v>
       </c>
       <c r="D184">
-        <v>1.997101783752441</v>
+        <v>1.928176164627075</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3807,7 +3807,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D185">
-        <v>1.056640863418579</v>
+        <v>1.306354522705078</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3821,7 +3821,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D186">
-        <v>1.084243535995483</v>
+        <v>1.144948482513428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3835,7 +3835,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D187">
-        <v>0.6233140230178833</v>
+        <v>0.6746509075164795</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3849,7 +3849,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D188">
-        <v>-0.06192129850387573</v>
+        <v>-0.1905530989170074</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3863,7 +3863,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D189">
-        <v>0.5641045570373535</v>
+        <v>0.3046700358390808</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3877,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="D190">
-        <v>3.086334705352783</v>
+        <v>2.675528764724731</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3891,7 +3891,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D191">
-        <v>3.816201686859131</v>
+        <v>3.579349040985107</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3905,7 +3905,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D192">
-        <v>2.150976181030273</v>
+        <v>2.616231441497803</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3919,7 +3919,7 @@
         <v>1.5</v>
       </c>
       <c r="D193">
-        <v>2.785013675689697</v>
+        <v>3.19185733795166</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3933,7 +3933,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>0.4820528030395508</v>
+        <v>-0.6441069841384888</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3947,7 +3947,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D195">
-        <v>1.765124082565308</v>
+        <v>2.431335687637329</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3961,7 +3961,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D196">
-        <v>1.713397741317749</v>
+        <v>1.621870398521423</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3975,7 +3975,7 @@
         <v>-6.5</v>
       </c>
       <c r="D197">
-        <v>-0.5735350251197815</v>
+        <v>-0.9863505363464355</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3989,7 +3989,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D198">
-        <v>3.659770727157593</v>
+        <v>2.659842252731323</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>0.8428935408592224</v>
+        <v>0.26022008061409</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4017,7 +4017,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D200">
-        <v>-0.1732469201087952</v>
+        <v>-0.1039538681507111</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4031,7 +4031,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D201">
-        <v>0.175494447350502</v>
+        <v>0.2131191790103912</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4045,7 +4045,7 @@
         <v>5.5</v>
       </c>
       <c r="D202">
-        <v>1.962611436843872</v>
+        <v>1.930893778800964</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4059,7 +4059,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D203">
-        <v>-1.877981424331665</v>
+        <v>-1.539980888366699</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4073,7 +4073,7 @@
         <v>1.5</v>
       </c>
       <c r="D204">
-        <v>2.088385820388794</v>
+        <v>1.56737756729126</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4087,7 +4087,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D205">
-        <v>-3.551602840423584</v>
+        <v>-4.200968742370605</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4101,7 +4101,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>-0.3222255706787109</v>
+        <v>-0.7161116600036621</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4115,7 +4115,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>2.10044527053833</v>
+        <v>2.949003934860229</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>0.6868394613265991</v>
+        <v>0.5661331415176392</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4143,7 +4143,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D209">
-        <v>0.991350531578064</v>
+        <v>1.478891253471375</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4157,7 +4157,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D210">
-        <v>0.2294542491436005</v>
+        <v>0.2091012895107269</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4171,7 +4171,7 @@
         <v>-2</v>
       </c>
       <c r="D211">
-        <v>-0.4065959453582764</v>
+        <v>0.6518881320953369</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4185,7 +4185,7 @@
         <v>-9.699999809265137</v>
       </c>
       <c r="D212">
-        <v>-6.540551662445068</v>
+        <v>-5.523159980773926</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4199,7 +4199,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D213">
-        <v>-0.1523897051811218</v>
+        <v>-0.6040849685668945</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4213,7 +4213,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D214">
-        <v>3.099478483200073</v>
+        <v>2.66494345664978</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4227,7 +4227,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D215">
-        <v>5.410811901092529</v>
+        <v>5.512489795684814</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4241,7 +4241,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D216">
-        <v>2.845426559448242</v>
+        <v>3.660403728485107</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4255,7 +4255,7 @@
         <v>9</v>
       </c>
       <c r="D217">
-        <v>1.44160270690918</v>
+        <v>1.705290794372559</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4269,7 +4269,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>3.546456336975098</v>
+        <v>2.522293329238892</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4283,7 +4283,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D219">
-        <v>3.333020210266113</v>
+        <v>3.446107864379883</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4297,7 +4297,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D220">
-        <v>-0.1859067678451538</v>
+        <v>0.4136699438095093</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4311,7 +4311,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D221">
-        <v>0.9789382219314575</v>
+        <v>1.370994329452515</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4325,7 +4325,7 @@
         <v>-3.5</v>
       </c>
       <c r="D222">
-        <v>0.5111336708068848</v>
+        <v>0.6438894271850586</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4339,7 +4339,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D223">
-        <v>0.4066944718360901</v>
+        <v>0.378867119550705</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4353,7 +4353,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D224">
-        <v>-3.46269154548645</v>
+        <v>-2.442678689956665</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4367,7 +4367,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D225">
-        <v>0.6094025373458862</v>
+        <v>0.04103296995162964</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4381,7 +4381,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D226">
-        <v>0.7255297899246216</v>
+        <v>0.8228286504745483</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4395,7 +4395,7 @@
         <v>-3.5</v>
       </c>
       <c r="D227">
-        <v>-0.9340329766273499</v>
+        <v>-1.722040414810181</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4409,7 +4409,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D228">
-        <v>-0.9426694512367249</v>
+        <v>-0.5388191938400269</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4423,7 +4423,7 @@
         <v>-11</v>
       </c>
       <c r="D229">
-        <v>-6.79644250869751</v>
+        <v>-5.859255313873291</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4437,7 +4437,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D230">
-        <v>1.388939380645752</v>
+        <v>1.233569622039795</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4451,7 +4451,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D231">
-        <v>0.5836105942726135</v>
+        <v>0.5694622993469238</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4465,7 +4465,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D232">
-        <v>-5.080634593963623</v>
+        <v>-4.493406772613525</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4479,7 +4479,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D233">
-        <v>0.8455197811126709</v>
+        <v>0.5002638101577759</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4493,7 +4493,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D234">
-        <v>-2.10636568069458</v>
+        <v>-1.79725980758667</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4507,7 +4507,7 @@
         <v>-0.5</v>
       </c>
       <c r="D235">
-        <v>1.040323972702026</v>
+        <v>1.55398964881897</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="D236">
-        <v>0.1481840163469315</v>
+        <v>0.1370177268981934</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4535,7 +4535,7 @@
         <v>-0.5</v>
       </c>
       <c r="D237">
-        <v>-1.376575231552124</v>
+        <v>-0.3127956390380859</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4549,7 +4549,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D238">
-        <v>-1.131200551986694</v>
+        <v>-0.8991491794586182</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4563,7 +4563,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D239">
-        <v>3.400627136230469</v>
+        <v>2.592482805252075</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4577,7 +4577,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D240">
-        <v>3.480244636535645</v>
+        <v>3.327666521072388</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4591,7 +4591,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D241">
-        <v>3.102514266967773</v>
+        <v>2.765184164047241</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4605,7 +4605,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D242">
-        <v>1.121656179428101</v>
+        <v>-0.05170920491218567</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4619,7 +4619,7 @@
         <v>3.5</v>
       </c>
       <c r="D243">
-        <v>0.2902528345584869</v>
+        <v>0.1581030040979385</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4633,7 +4633,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D244">
-        <v>3.02208948135376</v>
+        <v>2.745787382125854</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4647,7 +4647,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>0.2933700680732727</v>
+        <v>1.050571799278259</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4661,7 +4661,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D246">
-        <v>1.697211027145386</v>
+        <v>2.124302625656128</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>0.3823063671588898</v>
+        <v>0.2151704430580139</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4689,7 +4689,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D248">
-        <v>4.159725189208984</v>
+        <v>3.518494367599487</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4703,7 +4703,7 @@
         <v>20.5</v>
       </c>
       <c r="D249">
-        <v>-0.01004570722579956</v>
+        <v>0.06125906109809875</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4717,7 +4717,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D250">
-        <v>0.6348832249641418</v>
+        <v>0.9121887683868408</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4731,7 +4731,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D251">
-        <v>1.329935789108276</v>
+        <v>1.582126259803772</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4745,7 +4745,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D252">
-        <v>0.2286376804113388</v>
+        <v>0.3932036757469177</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4759,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>0.9905356168746948</v>
+        <v>2.159799814224243</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="D254">
-        <v>0.9745907187461853</v>
+        <v>1.174254179000854</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4787,7 +4787,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D255">
-        <v>3.446654796600342</v>
+        <v>1.855350494384766</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4801,7 +4801,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D256">
-        <v>4.164340972900391</v>
+        <v>4.22517728805542</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4815,7 +4815,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D257">
-        <v>1.723721027374268</v>
+        <v>1.46490490436554</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4829,7 +4829,7 @@
         <v>10.5</v>
       </c>
       <c r="D258">
-        <v>3.671558856964111</v>
+        <v>3.213653564453125</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4843,7 +4843,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D259">
-        <v>2.902163743972778</v>
+        <v>2.286670923233032</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4857,7 +4857,7 @@
         <v>1.5</v>
       </c>
       <c r="D260">
-        <v>-1.811946153640747</v>
+        <v>-1.018470048904419</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4871,7 +4871,7 @@
         <v>0.5</v>
       </c>
       <c r="D261">
-        <v>0.8108011484146118</v>
+        <v>0.9046183824539185</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4885,7 +4885,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D262">
-        <v>0.6172568798065186</v>
+        <v>0.4554186463356018</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4899,7 +4899,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D263">
-        <v>-0.2186132073402405</v>
+        <v>-0.4142209589481354</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4913,7 +4913,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D264">
-        <v>1.27679967880249</v>
+        <v>1.182242751121521</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4927,7 +4927,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D265">
-        <v>3.447350740432739</v>
+        <v>3.324727773666382</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4941,7 +4941,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D266">
-        <v>0.1915964782238007</v>
+        <v>0.6939171552658081</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4955,7 +4955,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D267">
-        <v>1.209755420684814</v>
+        <v>2.405383825302124</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4969,7 +4969,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D268">
-        <v>2.411422729492188</v>
+        <v>1.648383378982544</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4983,7 +4983,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D269">
-        <v>6.854255676269531</v>
+        <v>6.189148426055908</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4997,7 +4997,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D270">
-        <v>0.2829877734184265</v>
+        <v>0.4268049597740173</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5011,7 +5011,7 @@
         <v>-2.5</v>
       </c>
       <c r="D271">
-        <v>0.4224044680595398</v>
+        <v>0.6069408655166626</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5025,7 +5025,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D272">
-        <v>1.06536853313446</v>
+        <v>0.5926328897476196</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5039,7 +5039,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D273">
-        <v>-2.048054456710815</v>
+        <v>-2.043529987335205</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5053,7 +5053,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D274">
-        <v>-0.08613967895507812</v>
+        <v>0.1997689753770828</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5067,7 +5067,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D275">
-        <v>-0.819794237613678</v>
+        <v>-1.126493215560913</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5081,7 +5081,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D276">
-        <v>0.9746626019477844</v>
+        <v>0.3973285555839539</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5095,7 +5095,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>0.7404156923294067</v>
+        <v>0.6692953109741211</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5109,7 +5109,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D278">
-        <v>0.3062584400177002</v>
+        <v>0.3062049150466919</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5123,7 +5123,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D279">
-        <v>0.2629840075969696</v>
+        <v>0.1467741876840591</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D280">
-        <v>0.3038887679576874</v>
+        <v>0.6452089548110962</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5151,7 +5151,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D281">
-        <v>0.1023389101028442</v>
+        <v>0.1237486600875854</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5165,7 +5165,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D282">
-        <v>-0.6655827164649963</v>
+        <v>-0.9115207195281982</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5179,7 +5179,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D283">
-        <v>3.425925016403198</v>
+        <v>2.851122617721558</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5193,7 +5193,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D284">
-        <v>1.231276035308838</v>
+        <v>2.235879182815552</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5207,7 +5207,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D285">
-        <v>2.893066883087158</v>
+        <v>1.770370841026306</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5221,7 +5221,7 @@
         <v>2.5</v>
       </c>
       <c r="D286">
-        <v>-2.218851089477539</v>
+        <v>-2.259639501571655</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="D287">
-        <v>0.5513981580734253</v>
+        <v>0.2071036100387573</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5249,7 +5249,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D288">
-        <v>0.1289134472608566</v>
+        <v>-0.1445187628269196</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5263,7 +5263,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D289">
-        <v>1.906134366989136</v>
+        <v>0.8471184968948364</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>-0.09495598077774048</v>
+        <v>-0.267292320728302</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5291,7 +5291,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D291">
-        <v>-0.2922040224075317</v>
+        <v>-0.4425047934055328</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5305,7 +5305,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>-0.2103783488273621</v>
+        <v>-0.1096222698688507</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>-13.5</v>
       </c>
       <c r="D293">
-        <v>-4.473612308502197</v>
+        <v>-4.706933498382568</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5333,7 +5333,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D294">
-        <v>3.799729585647583</v>
+        <v>2.675968408584595</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5347,7 +5347,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D295">
-        <v>7.177023410797119</v>
+        <v>6.447022914886475</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D296">
-        <v>-0.7438933253288269</v>
+        <v>-0.2913537919521332</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5375,7 +5375,7 @@
         <v>5</v>
       </c>
       <c r="D297">
-        <v>1.925365447998047</v>
+        <v>2.123148441314697</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5389,7 +5389,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D298">
-        <v>0.860654890537262</v>
+        <v>0.6208741664886475</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5403,7 +5403,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D299">
-        <v>1.085653424263</v>
+        <v>1.484488725662231</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5417,7 +5417,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D300">
-        <v>2.377670526504517</v>
+        <v>2.316367626190186</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5431,7 +5431,7 @@
         <v>-8</v>
       </c>
       <c r="D301">
-        <v>-9.068943977355957</v>
+        <v>-8.013400077819824</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5445,7 +5445,7 @@
         <v>0.5</v>
       </c>
       <c r="D302">
-        <v>3.432931900024414</v>
+        <v>3.040209531784058</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5459,7 +5459,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D303">
-        <v>1.51113224029541</v>
+        <v>0.9093633890151978</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5473,7 +5473,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D304">
-        <v>0.1740568429231644</v>
+        <v>-0.03668865561485291</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5487,7 +5487,7 @@
         <v>3</v>
       </c>
       <c r="D305">
-        <v>0.7798423171043396</v>
+        <v>1.279526472091675</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5501,7 +5501,7 @@
         <v>5</v>
       </c>
       <c r="D306">
-        <v>-0.2666602730751038</v>
+        <v>0.1694207191467285</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5515,7 +5515,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D307">
-        <v>-3.877043724060059</v>
+        <v>-3.076728105545044</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5529,7 +5529,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D308">
-        <v>0.3265581727027893</v>
+        <v>0.2439656257629395</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5543,7 +5543,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D309">
-        <v>2.719444274902344</v>
+        <v>2.695286750793457</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5557,7 +5557,7 @@
         <v>1.5</v>
       </c>
       <c r="D310">
-        <v>0.5323925614356995</v>
+        <v>0.3088878393173218</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5571,7 +5571,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D311">
-        <v>0.6149688363075256</v>
+        <v>-0.4495728313922882</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5585,7 +5585,7 @@
         <v>-0.5</v>
       </c>
       <c r="D312">
-        <v>0.1884114593267441</v>
+        <v>0.6639242172241211</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5599,7 +5599,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D313">
-        <v>-0.1847726702690125</v>
+        <v>0.5797525644302368</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D314">
-        <v>0.5890001058578491</v>
+        <v>0.8873476982116699</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5627,7 +5627,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D315">
-        <v>-1.359695911407471</v>
+        <v>-0.4987843930721283</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5641,7 +5641,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D316">
-        <v>0.1432769596576691</v>
+        <v>0.3260538280010223</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5655,7 +5655,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D317">
-        <v>5.947481632232666</v>
+        <v>5.370504856109619</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5669,7 +5669,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D318">
-        <v>2.740528106689453</v>
+        <v>3.693461179733276</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5683,7 +5683,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D319">
-        <v>-1.117402076721191</v>
+        <v>-0.2079109251499176</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5697,7 +5697,7 @@
         <v>4</v>
       </c>
       <c r="D320">
-        <v>-0.8533053994178772</v>
+        <v>-0.7919877767562866</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5711,7 +5711,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D321">
-        <v>1.105072498321533</v>
+        <v>1.334412693977356</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5725,7 +5725,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D322">
-        <v>1.341028213500977</v>
+        <v>2.085167407989502</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5739,7 +5739,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D323">
-        <v>0.9350163340568542</v>
+        <v>1.454441666603088</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5753,7 +5753,7 @@
         <v>2</v>
       </c>
       <c r="D324">
-        <v>0.6657965183258057</v>
+        <v>0.2236241549253464</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5767,7 +5767,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D325">
-        <v>-0.01169973611831665</v>
+        <v>-0.622542142868042</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5781,7 +5781,7 @@
         <v>-6</v>
       </c>
       <c r="D326">
-        <v>-3.152098655700684</v>
+        <v>-4.451046466827393</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5795,7 +5795,7 @@
         <v>1.5</v>
       </c>
       <c r="D327">
-        <v>0.5810884237289429</v>
+        <v>0.4288824796676636</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5809,7 +5809,7 @@
         <v>3.5</v>
       </c>
       <c r="D328">
-        <v>2.335738658905029</v>
+        <v>2.012367486953735</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5823,7 +5823,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D329">
-        <v>1.270900011062622</v>
+        <v>1.669247508049011</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5837,7 +5837,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D330">
-        <v>-0.02308464050292969</v>
+        <v>-0.03619064390659332</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5851,7 +5851,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D331">
-        <v>-2.843050956726074</v>
+        <v>-2.860011577606201</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5865,7 +5865,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>1.989800214767456</v>
+        <v>1.841575145721436</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5879,7 +5879,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D333">
-        <v>-0.3252259492874146</v>
+        <v>0.3173149824142456</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5893,7 +5893,7 @@
         <v>7.5</v>
       </c>
       <c r="D334">
-        <v>4.038232326507568</v>
+        <v>3.249443769454956</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5907,7 +5907,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D335">
-        <v>0.02837547659873962</v>
+        <v>0.1903417408466339</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5921,7 +5921,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D336">
-        <v>0.709196150302887</v>
+        <v>0.2358938157558441</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5935,7 +5935,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D337">
-        <v>0.346684992313385</v>
+        <v>0.127537414431572</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5949,7 +5949,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D338">
-        <v>0.2848230600357056</v>
+        <v>0.8928284645080566</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5963,7 +5963,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D339">
-        <v>0.5140295028686523</v>
+        <v>0.603891909122467</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5977,7 +5977,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D340">
-        <v>-4.554549694061279</v>
+        <v>-4.395127773284912</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5991,7 +5991,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>1.467347860336304</v>
+        <v>0.9380526542663574</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6005,7 +6005,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D342">
-        <v>-0.0355927050113678</v>
+        <v>0.1604143679141998</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6019,7 +6019,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D343">
-        <v>-0.4906038641929626</v>
+        <v>-1.086244106292725</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6033,7 +6033,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D344">
-        <v>-0.5965681672096252</v>
+        <v>-0.3525457680225372</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6047,7 +6047,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D345">
-        <v>0.3518237471580505</v>
+        <v>0.3992055058479309</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6061,7 +6061,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D346">
-        <v>-0.0796923041343689</v>
+        <v>-0.09186533093452454</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6075,7 +6075,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D347">
-        <v>4.646225452423096</v>
+        <v>3.702439069747925</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6089,7 +6089,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D348">
-        <v>1.554641485214233</v>
+        <v>1.752432107925415</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6103,7 +6103,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D349">
-        <v>1.611611366271973</v>
+        <v>1.131752729415894</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6117,7 +6117,7 @@
         <v>4</v>
       </c>
       <c r="D350">
-        <v>3.751514673233032</v>
+        <v>3.432268857955933</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6131,7 +6131,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D351">
-        <v>0.3094232678413391</v>
+        <v>1.429121851921082</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6145,7 +6145,7 @@
         <v>-3</v>
       </c>
       <c r="D352">
-        <v>-2.697864055633545</v>
+        <v>-0.7905962467193604</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6159,7 +6159,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>1.080317735671997</v>
+        <v>1.475364446640015</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6173,7 +6173,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D354">
-        <v>0.2526730298995972</v>
+        <v>0.1822447329759598</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6187,7 +6187,7 @@
         <v>4</v>
       </c>
       <c r="D355">
-        <v>1.591456890106201</v>
+        <v>1.530746579170227</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6201,7 +6201,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D356">
-        <v>5.241825103759766</v>
+        <v>3.654066562652588</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6215,7 +6215,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D357">
-        <v>6.499120712280273</v>
+        <v>6.069094181060791</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6229,7 +6229,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D358">
-        <v>-0.8446611762046814</v>
+        <v>-0.6563953161239624</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6243,7 +6243,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D359">
-        <v>0.4190690219402313</v>
+        <v>0.8244225978851318</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6257,7 +6257,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D360">
-        <v>-0.02064990997314453</v>
+        <v>-0.01882395148277283</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="D361">
-        <v>2.538783550262451</v>
+        <v>1.800992250442505</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6285,7 +6285,7 @@
         <v>-2.5</v>
       </c>
       <c r="D362">
-        <v>0.3197559714317322</v>
+        <v>0.2459642291069031</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6299,7 +6299,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D363">
-        <v>2.05269193649292</v>
+        <v>2.741727590560913</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6313,7 +6313,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D364">
-        <v>0.1523979306221008</v>
+        <v>-0.05638006329536438</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6327,7 +6327,7 @@
         <v>-12.89999961853027</v>
       </c>
       <c r="D365">
-        <v>-2.924783229827881</v>
+        <v>-5.465962886810303</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6341,7 +6341,7 @@
         <v>2.5</v>
       </c>
       <c r="D366">
-        <v>2.556674957275391</v>
+        <v>1.938468337059021</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6355,7 +6355,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D367">
-        <v>0.8284280896186829</v>
+        <v>1.679840326309204</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6369,7 +6369,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D368">
-        <v>1.907808780670166</v>
+        <v>2.387973546981812</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6383,7 +6383,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D369">
-        <v>1.514971971511841</v>
+        <v>0.2763635218143463</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6397,7 +6397,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D370">
-        <v>-8.506669044494629</v>
+        <v>-8.942155838012695</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6411,7 +6411,7 @@
         <v>3.5</v>
       </c>
       <c r="D371">
-        <v>2.520561695098877</v>
+        <v>3.383241891860962</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6425,7 +6425,7 @@
         <v>0.5</v>
       </c>
       <c r="D372">
-        <v>1.102439880371094</v>
+        <v>1.070676922798157</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6439,7 +6439,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D373">
-        <v>-3.158969879150391</v>
+        <v>-3.199918508529663</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6453,7 +6453,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D374">
-        <v>1.014857053756714</v>
+        <v>0.7495049238204956</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6467,7 +6467,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D375">
-        <v>1.881821155548096</v>
+        <v>2.83178448677063</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6481,7 +6481,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D376">
-        <v>1.140705823898315</v>
+        <v>1.081323504447937</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6495,7 +6495,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D377">
-        <v>0.6448278427124023</v>
+        <v>0.4220519959926605</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6509,7 +6509,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D378">
-        <v>2.626487255096436</v>
+        <v>3.062752723693848</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6523,7 +6523,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D379">
-        <v>-1.19928765296936</v>
+        <v>-2.360018491744995</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6537,7 +6537,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D380">
-        <v>0.05716758966445923</v>
+        <v>0.1585971415042877</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6551,7 +6551,7 @@
         <v>-2</v>
       </c>
       <c r="D381">
-        <v>0.2288693487644196</v>
+        <v>0.08515996485948563</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6565,7 +6565,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D382">
-        <v>-1.76973295211792</v>
+        <v>-2.535752534866333</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6579,7 +6579,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D383">
-        <v>0.04979372024536133</v>
+        <v>0.05029869079589844</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6593,7 +6593,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D384">
-        <v>-1.791834115982056</v>
+        <v>-2.59285569190979</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6607,7 +6607,7 @@
         <v>3.5</v>
       </c>
       <c r="D385">
-        <v>1.408821821212769</v>
+        <v>1.516730546951294</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6621,7 +6621,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D386">
-        <v>1.657438993453979</v>
+        <v>2.111056566238403</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6635,7 +6635,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>1.832717180252075</v>
+        <v>1.295976996421814</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6649,7 +6649,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D388">
-        <v>0.3193355798721313</v>
+        <v>0.3268358111381531</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6663,7 +6663,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D389">
-        <v>-0.535224437713623</v>
+        <v>-0.06425391137599945</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6677,7 +6677,7 @@
         <v>2.5</v>
       </c>
       <c r="D390">
-        <v>0.2072825580835342</v>
+        <v>0.1748352348804474</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6691,7 +6691,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D391">
-        <v>0.7965394854545593</v>
+        <v>0.8912737369537354</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6705,7 +6705,7 @@
         <v>-1.5</v>
       </c>
       <c r="D392">
-        <v>0.1586107015609741</v>
+        <v>0.9116338491439819</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6719,7 +6719,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D393">
-        <v>-0.2704589366912842</v>
+        <v>-0.3836713135242462</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6733,7 +6733,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D394">
-        <v>0.6923945546150208</v>
+        <v>0.8939883708953857</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6747,7 +6747,7 @@
         <v>-1.5</v>
       </c>
       <c r="D395">
-        <v>-0.2600013613700867</v>
+        <v>0.02398085594177246</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6761,7 +6761,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D396">
-        <v>1.410892724990845</v>
+        <v>1.444461584091187</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6775,7 +6775,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D397">
-        <v>1.061822652816772</v>
+        <v>0.7019075155258179</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6789,7 +6789,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D398">
-        <v>3.4982008934021</v>
+        <v>3.156310796737671</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6803,7 +6803,7 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>0.9035577178001404</v>
+        <v>0.864435076713562</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6817,7 +6817,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D400">
-        <v>2.825924873352051</v>
+        <v>4.159022331237793</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6831,7 +6831,7 @@
         <v>4</v>
       </c>
       <c r="D401">
-        <v>3.466354608535767</v>
+        <v>2.647360563278198</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6845,7 +6845,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D402">
-        <v>0.6814544200897217</v>
+        <v>0.1800229847431183</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6859,7 +6859,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D403">
-        <v>0.7661514282226562</v>
+        <v>0.9264001846313477</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6873,7 +6873,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D404">
-        <v>0.4640720188617706</v>
+        <v>1.145851612091064</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6887,7 +6887,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D405">
-        <v>0.7542992234230042</v>
+        <v>0.475102037191391</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6901,7 +6901,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D406">
-        <v>1.754978179931641</v>
+        <v>1.831469058990479</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6915,7 +6915,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D407">
-        <v>0.7355837225914001</v>
+        <v>0.8592519760131836</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6929,7 +6929,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D408">
-        <v>2.695675134658813</v>
+        <v>2.732831716537476</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6943,7 +6943,7 @@
         <v>4.5</v>
       </c>
       <c r="D409">
-        <v>1.066784143447876</v>
+        <v>1.009145975112915</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6957,7 +6957,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D410">
-        <v>0.454487532377243</v>
+        <v>1.105059623718262</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6971,7 +6971,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D411">
-        <v>-0.5376365780830383</v>
+        <v>-0.6586178541183472</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6985,7 +6985,7 @@
         <v>6.5</v>
       </c>
       <c r="D412">
-        <v>3.968550682067871</v>
+        <v>3.374377965927124</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6999,7 +6999,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D413">
-        <v>0.8313801288604736</v>
+        <v>2.78469443321228</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7013,7 +7013,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D414">
-        <v>1.472261190414429</v>
+        <v>1.871783852577209</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7027,7 +7027,7 @@
         <v>-3.5</v>
       </c>
       <c r="D415">
-        <v>-0.7933602929115295</v>
+        <v>-1.039371967315674</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7041,7 +7041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D416">
-        <v>6.974429607391357</v>
+        <v>7.743092060089111</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7055,7 +7055,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D417">
-        <v>3.999831676483154</v>
+        <v>3.516028165817261</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7069,7 +7069,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D418">
-        <v>-0.4246291518211365</v>
+        <v>-0.8592977523803711</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7083,7 +7083,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D419">
-        <v>0.3361768126487732</v>
+        <v>0.1980747133493423</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7097,7 +7097,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D420">
-        <v>1.360980987548828</v>
+        <v>1.181123018264771</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7111,7 +7111,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D421">
-        <v>1.508310317993164</v>
+        <v>1.881010293960571</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7125,7 +7125,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D422">
-        <v>1.0601487159729</v>
+        <v>1.466707587242126</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7139,7 +7139,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D423">
-        <v>3.044451236724854</v>
+        <v>2.65192174911499</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="D424">
-        <v>0.5057957172393799</v>
+        <v>0.1818309873342514</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7167,7 +7167,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D425">
-        <v>0.4394371211528778</v>
+        <v>0.2510707676410675</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="D426">
-        <v>3.315714836120605</v>
+        <v>2.946347951889038</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7195,7 +7195,7 @@
         <v>-0.5</v>
       </c>
       <c r="D427">
-        <v>1.013146877288818</v>
+        <v>0.4083923697471619</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7209,7 +7209,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D428">
-        <v>-0.04277831315994263</v>
+        <v>-0.1983316242694855</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7223,7 +7223,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>3.091738700866699</v>
+        <v>2.504928588867188</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7237,7 +7237,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D430">
-        <v>3.955052137374878</v>
+        <v>3.167923212051392</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7251,7 +7251,7 @@
         <v>-0.5</v>
       </c>
       <c r="D431">
-        <v>0.2019271403551102</v>
+        <v>0.5810384750366211</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7265,7 +7265,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D432">
-        <v>1.029183626174927</v>
+        <v>1.168833017349243</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7279,7 +7279,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>1.789159059524536</v>
+        <v>1.801845192909241</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7293,7 +7293,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>-0.1042815148830414</v>
+        <v>-0.3915210068225861</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7307,7 +7307,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D435">
-        <v>2.78788423538208</v>
+        <v>3.613648176193237</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7321,7 +7321,7 @@
         <v>-0.5</v>
       </c>
       <c r="D436">
-        <v>-2.163948059082031</v>
+        <v>-1.557039260864258</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7335,7 +7335,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D437">
-        <v>0.5858058929443359</v>
+        <v>0.3926882445812225</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7349,7 +7349,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D438">
-        <v>1.235711097717285</v>
+        <v>1.162096977233887</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7363,7 +7363,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D439">
-        <v>-0.554972231388092</v>
+        <v>-0.61761474609375</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7377,7 +7377,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D440">
-        <v>0.9989650249481201</v>
+        <v>1.001976847648621</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7391,7 +7391,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D441">
-        <v>-1.243556976318359</v>
+        <v>-0.7412501573562622</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7405,7 +7405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D442">
-        <v>0.3309829533100128</v>
+        <v>0.3238532543182373</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7419,7 +7419,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D443">
-        <v>3.322339773178101</v>
+        <v>3.614233255386353</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7433,7 +7433,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D444">
-        <v>2.72357177734375</v>
+        <v>2.921050310134888</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7447,7 +7447,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D445">
-        <v>0.4829229712486267</v>
+        <v>0.1742253005504608</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7461,7 +7461,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D446">
-        <v>-0.4125165343284607</v>
+        <v>-0.3045431077480316</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7475,7 +7475,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D447">
-        <v>0.5964727401733398</v>
+        <v>0.2386550456285477</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7489,7 +7489,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D448">
-        <v>4.717939853668213</v>
+        <v>4.454562664031982</v>
       </c>
     </row>
   </sheetData>
